--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-familymemberhistory.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-familymemberhistory.xlsx
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>このプロファイルはFamilyMemberHistoryリソースに対して、データを送受信するための共通の制約と拡張を定めたものである。</t>
+    <t>このプロファイルはFamilyMemberHistoryリソースに対して、患者の家族歴のデータを送受信するための共通の制約と拡張を定めたものである。</t>
   </si>
   <si>
     <t>Purpose</t>
